--- a/branches/dev/StructureDefinition-mii-pr-icu-bilanz-ausfuhr-haemofiltration-einzelmesswerte.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-icu-bilanz-ausfuhr-haemofiltration-einzelmesswerte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T15:49:26+00:00</t>
+    <t>2026-10-20T13:26:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-icu-bilanz-ausfuhr-haemofiltration-einzelmesswerte.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-icu-bilanz-ausfuhr-haemofiltration-einzelmesswerte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T13:26:59+00:00</t>
+    <t>2026-10-20T13:56:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-icu-bilanz-ausfuhr-haemofiltration-einzelmesswerte.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-icu-bilanz-ausfuhr-haemofiltration-einzelmesswerte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T13:56:55+00:00</t>
+    <t>2026-10-29T10:59:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
